--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268227</v>
+        <v>121268834</v>
       </c>
       <c r="B5" t="n">
-        <v>97018</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372338</v>
+        <v>372211</v>
       </c>
       <c r="R5" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268458</v>
+        <v>121268227</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>97028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372327</v>
+        <v>372338</v>
       </c>
       <c r="R6" t="n">
         <v>6615886</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268834</v>
+        <v>121268458</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372211</v>
+        <v>372327</v>
       </c>
       <c r="R7" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268834</v>
+        <v>121268227</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>97028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372211</v>
+        <v>372338</v>
       </c>
       <c r="R5" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268227</v>
+        <v>121268458</v>
       </c>
       <c r="B6" t="n">
-        <v>97028</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372338</v>
+        <v>372327</v>
       </c>
       <c r="R6" t="n">
         <v>6615886</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,7 +1326,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268458</v>
+        <v>121268834</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372327</v>
+        <v>372211</v>
       </c>
       <c r="R7" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268227</v>
+        <v>121268458</v>
       </c>
       <c r="B5" t="n">
-        <v>97028</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372338</v>
+        <v>372327</v>
       </c>
       <c r="R5" t="n">
         <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268458</v>
+        <v>121268834</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372327</v>
+        <v>372211</v>
       </c>
       <c r="R6" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268834</v>
+        <v>121268227</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>97041</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372211</v>
+        <v>372338</v>
       </c>
       <c r="R7" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,6 +1440,238 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121489162</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>372192</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6615979</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>S-Arv-0604</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isabel Gunn, Victor Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121489163</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>372274</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6615840</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>S-Arv-0603</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268458</v>
+        <v>121268227</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>97042</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372327</v>
+        <v>372338</v>
       </c>
       <c r="R5" t="n">
         <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268834</v>
+        <v>121268458</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372211</v>
+        <v>372327</v>
       </c>
       <c r="R6" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268227</v>
+        <v>121268834</v>
       </c>
       <c r="B7" t="n">
-        <v>97041</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372338</v>
+        <v>372211</v>
       </c>
       <c r="R7" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,7 +1446,7 @@
         <v>121489162</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>121489163</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>121268227</v>
       </c>
       <c r="B5" t="n">
-        <v>97042</v>
+        <v>97045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>121268458</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>121268834</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>121489162</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>121489163</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268227</v>
+        <v>121268458</v>
       </c>
       <c r="B5" t="n">
-        <v>97045</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372338</v>
+        <v>372327</v>
       </c>
       <c r="R5" t="n">
         <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268458</v>
+        <v>121268834</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372327</v>
+        <v>372211</v>
       </c>
       <c r="R6" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268834</v>
+        <v>121268227</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>97045</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372211</v>
+        <v>372338</v>
       </c>
       <c r="R7" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,7 +1443,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1479,17 +1479,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R8" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1559,7 +1559,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121489163</v>
+        <v>121489162</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1595,17 +1595,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372274</v>
+        <v>372192</v>
       </c>
       <c r="R9" t="n">
-        <v>6615840</v>
+        <v>6615979</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>S-Arv-0603</t>
+          <t>S-Arv-0604</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Isabel Gunn, Victor Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268458</v>
+        <v>121268834</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372327</v>
+        <v>372211</v>
       </c>
       <c r="R5" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268834</v>
+        <v>121268458</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372211</v>
+        <v>372327</v>
       </c>
       <c r="R6" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
         <v>121268227</v>
       </c>
       <c r="B7" t="n">
-        <v>97045</v>
+        <v>97051</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489163</v>
+        <v>121489162</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,17 +1479,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372274</v>
+        <v>372192</v>
       </c>
       <c r="R8" t="n">
-        <v>6615840</v>
+        <v>6615979</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0603</t>
+          <t>S-Arv-0604</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Isabel Gunn, Victor Pettersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,17 +1595,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R9" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268834</v>
+        <v>121268227</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372211</v>
+        <v>372338</v>
       </c>
       <c r="R5" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268458</v>
+        <v>121268834</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372327</v>
+        <v>372211</v>
       </c>
       <c r="R6" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268227</v>
+        <v>121268458</v>
       </c>
       <c r="B7" t="n">
-        <v>97051</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372338</v>
+        <v>372327</v>
       </c>
       <c r="R7" t="n">
         <v>6615886</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,17 +1479,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R8" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121489163</v>
+        <v>121489162</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,17 +1595,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372274</v>
+        <v>372192</v>
       </c>
       <c r="R9" t="n">
-        <v>6615840</v>
+        <v>6615979</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>S-Arv-0603</t>
+          <t>S-Arv-0604</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Isabel Gunn, Victor Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268227</v>
+        <v>121268458</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372338</v>
+        <v>372327</v>
       </c>
       <c r="R5" t="n">
         <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268458</v>
+        <v>121268227</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>97052</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372327</v>
+        <v>372338</v>
       </c>
       <c r="R7" t="n">
         <v>6615886</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268458</v>
+        <v>121268227</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6052779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372327</v>
+        <v>372338</v>
       </c>
       <c r="R5" t="n">
         <v>6615886</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>Intill stigen vid en hyfs att stor blödande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268834</v>
+        <v>121268458</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372211</v>
+        <v>372327</v>
       </c>
       <c r="R6" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268227</v>
+        <v>121268834</v>
       </c>
       <c r="B7" t="n">
-        <v>97052</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372338</v>
+        <v>372211</v>
       </c>
       <c r="R7" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,7 +1443,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489163</v>
+        <v>121489162</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1479,17 +1479,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372274</v>
+        <v>372192</v>
       </c>
       <c r="R8" t="n">
-        <v>6615840</v>
+        <v>6615979</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0603</t>
+          <t>S-Arv-0604</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Isabel Gunn, Victor Pettersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1559,7 +1559,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1595,17 +1595,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R9" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268458</v>
+        <v>121268834</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372327</v>
+        <v>372211</v>
       </c>
       <c r="R6" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,7 +1326,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268834</v>
+        <v>121268458</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372211</v>
+        <v>372327</v>
       </c>
       <c r="R7" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,7 +1443,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1479,17 +1479,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R8" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1559,7 +1559,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121489163</v>
+        <v>121489162</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1595,17 +1595,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372274</v>
+        <v>372192</v>
       </c>
       <c r="R9" t="n">
-        <v>6615840</v>
+        <v>6615979</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>S-Arv-0603</t>
+          <t>S-Arv-0604</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Isabel Gunn, Victor Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -1443,10 +1443,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489163</v>
+        <v>121489162</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,17 +1479,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372274</v>
+        <v>372192</v>
       </c>
       <c r="R8" t="n">
-        <v>6615840</v>
+        <v>6615979</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0603</t>
+          <t>S-Arv-0604</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Isabel Gunn, Victor Pettersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,17 +1595,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R9" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121268227</v>
+        <v>121268834</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372338</v>
+        <v>372211</v>
       </c>
       <c r="R5" t="n">
-        <v>6615886</v>
+        <v>6615904</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Intill stigen vid en hyfs att stor blödande gran</t>
+          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121268834</v>
+        <v>121268458</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372211</v>
+        <v>372327</v>
       </c>
       <c r="R6" t="n">
-        <v>6615904</v>
+        <v>6615886</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>100 m vänster om stigen. Nerför en stor mosstäckt bumling. Skogen här är blandat med mycket grövre tallar och mycket ungt också. Flera gamla och döda en träd.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121268458</v>
+        <v>121489162</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,17 +1362,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örnfjället, Örnfjället, Vrm</t>
+          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372327</v>
+        <v>372192</v>
       </c>
       <c r="R7" t="n">
-        <v>6615886</v>
+        <v>6615979</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,29 +1394,24 @@
           <t>Arvika</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>S-Arv-0604</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling.</t>
+          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,19 +1426,23 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Isabel Gunn, Victor Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489162</v>
+        <v>121489163</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1479,17 +1478,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
+          <t>Fåängen, 600 m NNÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372192</v>
+        <v>372274</v>
       </c>
       <c r="R8" t="n">
-        <v>6615979</v>
+        <v>6615840</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,7 +1512,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>S-Arv-0604</t>
+          <t>S-Arv-0603</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1528,7 +1527,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
+          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,126 +1547,10 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>121489163</v>
-      </c>
-      <c r="B9" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>372274</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6615840</v>
-      </c>
-      <c r="S9" t="n">
-        <v>50</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>S-Arv-0603</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Isabel Gunn</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 47217-2024 artfynd.xlsx
+++ b/artfynd/A 47217-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1324,238 +1324,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>121489162</v>
-      </c>
-      <c r="B7" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Fåängen, 700 m N-NNÖ om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>372192</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6615979</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>S-Arv-0604</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rapporterad från RT90: 6619750 - 1326798, 21 m noggrannhet av Isabel Gunn resp. 6619770 - 1326847, 5 m noggrannhet av Victor Pettersson.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Isabel Gunn, Victor Pettersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>121489163</v>
-      </c>
-      <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Fåängen, 600 m NNÖ om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>372274</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6615840</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>S-Arv-0603</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vänster sidan av stigen. Lite nerför en höfthöjdsbumling. Rapporterad koordinat RT90: 6619731 - 1326914, 30 moggrannhet.</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Isabel Gunn</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
